--- a/companies/kmw/model.xlsx
+++ b/companies/kmw/model.xlsx
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cb64f5beda7cb937</t>
+          <t>8f705741067cf5d4</t>
         </is>
       </c>
     </row>
